--- a/static/plantilla_resumen_cuit.xlsx
+++ b/static/plantilla_resumen_cuit.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lucas\Cursor Programacion\Depuracion Excel Mis Comprobantes ENLACE ARCA\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lucas\Cursor Programacion\Analisis Integral del Contribuyente\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8520" windowHeight="10230" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="8520" windowHeight="10230"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos" sheetId="1" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" r:id="rId2"/>
+    <sheet name="Resumen" sheetId="2" r:id="rId1"/>
+    <sheet name="Datos" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>CUIT</t>
   </si>
@@ -45,6 +45,9 @@
     <t>Neto Gravado Total</t>
   </si>
   <si>
+    <t>Ingresos no grav. y exentos</t>
+  </si>
+  <si>
     <t>Total IVA</t>
   </si>
   <si>
@@ -73,6 +76,9 @@
   </si>
   <si>
     <t>Σ Neto Gravado Total</t>
+  </si>
+  <si>
+    <t>Σ Ingresos no grav. y exentos</t>
   </si>
   <si>
     <t>Σ Total IVA</t>
@@ -127,7 +133,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \(#,##0.00\)_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \(#,##0.00\)_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
@@ -151,11 +160,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="Usuario" refreshedDate="46176.952131944447" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="Usuario" refreshedDate="46188.593594444443" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
   <cacheSource type="worksheet">
     <worksheetSource name="TablaDatos"/>
   </cacheSource>
-  <cacheFields count="7">
+  <cacheFields count="8">
     <cacheField name="CUIT" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20000000001" maxValue="20000000002" count="2">
         <n v="20000000001"/>
@@ -180,6 +189,9 @@
     <cacheField name="Neto Gravado Total" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="500" maxValue="2000"/>
     </cacheField>
+    <cacheField name="Ingresos no grav. y exentos" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="80" maxValue="200"/>
+    </cacheField>
     <cacheField name="Total IVA" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="105" maxValue="420"/>
     </cacheField>
@@ -203,6 +215,7 @@
     <x v="0"/>
     <s v="2025-01"/>
     <n v="1000"/>
+    <n v="150"/>
     <n v="210"/>
     <n v="1210"/>
   </r>
@@ -212,6 +225,7 @@
     <x v="1"/>
     <s v="2025-01"/>
     <n v="500"/>
+    <n v="80"/>
     <n v="105"/>
     <n v="605"/>
   </r>
@@ -221,6 +235,7 @@
     <x v="0"/>
     <s v="2025-02"/>
     <n v="2000"/>
+    <n v="200"/>
     <n v="420"/>
     <n v="2420"/>
   </r>
@@ -229,8 +244,8 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ResumenCUIT" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:H6" firstHeaderRow="1" firstDataRow="3" firstDataCol="2"/>
-  <pivotFields count="7">
+  <location ref="A1:J6" firstHeaderRow="1" firstDataRow="3" firstDataCol="2"/>
+  <pivotFields count="8">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="2">
         <item x="0"/>
@@ -293,6 +308,13 @@
         </ext>
       </extLst>
     </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
@@ -315,7 +337,7 @@
     <field x="2"/>
     <field x="-2"/>
   </colFields>
-  <colItems count="6">
+  <colItems count="8">
     <i>
       <x/>
       <x/>
@@ -326,6 +348,9 @@
     <i r="1" i="2">
       <x v="2"/>
     </i>
+    <i r="1" i="3">
+      <x v="3"/>
+    </i>
     <i>
       <x v="1"/>
       <x/>
@@ -336,11 +361,15 @@
     <i r="1" i="2">
       <x v="2"/>
     </i>
+    <i r="1" i="3">
+      <x v="3"/>
+    </i>
   </colItems>
-  <dataFields count="3">
+  <dataFields count="4">
     <dataField name="Σ Neto Gravado Total" fld="4" baseField="0" baseItem="0" numFmtId="164"/>
-    <dataField name="Σ Total IVA" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
-    <dataField name="Σ Imp. Total" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Σ Ingresos no grav. y exentos" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Σ Total IVA" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Σ Imp. Total" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -352,16 +381,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaDatos" displayName="TablaDatos" ref="A1:G4" totalsRowShown="0">
-  <autoFilter ref="A1:G4"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaDatos" displayName="TablaDatos" ref="A1:H4" totalsRowShown="0">
+  <autoFilter ref="A1:H4"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="CUIT"/>
     <tableColumn id="2" name="Razón Social"/>
     <tableColumn id="3" name="Tipo"/>
     <tableColumn id="4" name="Mes"/>
-    <tableColumn id="5" name="Neto Gravado Total" dataDxfId="2"/>
-    <tableColumn id="6" name="Total IVA" dataDxfId="1"/>
-    <tableColumn id="7" name="Imp. Total" dataDxfId="0"/>
+    <tableColumn id="5" name="Neto Gravado Total" dataDxfId="3"/>
+    <tableColumn id="6" name="Ingresos no grav. y exentos" dataDxfId="2"/>
+    <tableColumn id="7" name="Total IVA" dataDxfId="1"/>
+    <tableColumn id="8" name="Imp. Total" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -630,16 +660,188 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.625" customWidth="1"/>
+    <col min="3" max="9" width="27.375" customWidth="1"/>
+    <col min="10" max="10" width="27.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.125" customWidth="1"/>
+    <col min="12" max="12" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="14" max="14" width="16.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>20000000001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D4" s="2">
+        <v>150</v>
+      </c>
+      <c r="E4" s="2">
+        <v>210</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1210</v>
+      </c>
+      <c r="G4" s="2">
+        <v>500</v>
+      </c>
+      <c r="H4" s="2">
+        <v>80</v>
+      </c>
+      <c r="I4" s="2">
+        <v>105</v>
+      </c>
+      <c r="J4" s="2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>20000000002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2000</v>
+      </c>
+      <c r="D5" s="2">
+        <v>200</v>
+      </c>
+      <c r="E5" s="2">
+        <v>420</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2420</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3000</v>
+      </c>
+      <c r="D6" s="2">
+        <v>350</v>
+      </c>
+      <c r="E6" s="2">
+        <v>630</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3630</v>
+      </c>
+      <c r="G6" s="2">
+        <v>500</v>
+      </c>
+      <c r="H6" s="2">
+        <v>80</v>
+      </c>
+      <c r="I6" s="2">
+        <v>105</v>
+      </c>
+      <c r="J6" s="2">
+        <v>605</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.25" customWidth="1"/>
     <col min="5" max="5" width="20.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11" style="2"/>
-    <col min="7" max="7" width="11.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="27.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2"/>
+    <col min="8" max="8" width="11.375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -661,73 +863,85 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>20000000001</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2">
         <v>1000</v>
       </c>
       <c r="F2" s="2">
+        <v>150</v>
+      </c>
+      <c r="G2" s="2">
         <v>210</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>1210</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>20000000001</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
       </c>
       <c r="E3" s="2">
         <v>500</v>
       </c>
       <c r="F3" s="2">
+        <v>80</v>
+      </c>
+      <c r="G3" s="2">
         <v>105</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>605</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>20000000002</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2">
         <v>2000</v>
       </c>
       <c r="F4" s="2">
+        <v>200</v>
+      </c>
+      <c r="G4" s="2">
         <v>420</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>2420</v>
       </c>
     </row>
@@ -737,145 +951,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="23.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.625" customWidth="1"/>
-    <col min="3" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="25.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.25" customWidth="1"/>
-    <col min="11" max="11" width="16.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>20000000001</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D4" s="2">
-        <v>210</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1210</v>
-      </c>
-      <c r="F4" s="2">
-        <v>500</v>
-      </c>
-      <c r="G4" s="2">
-        <v>105</v>
-      </c>
-      <c r="H4" s="2">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>20000000002</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2000</v>
-      </c>
-      <c r="D5" s="2">
-        <v>420</v>
-      </c>
-      <c r="E5" s="2">
-        <v>2420</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2">
-        <v>3000</v>
-      </c>
-      <c r="D6" s="2">
-        <v>630</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3630</v>
-      </c>
-      <c r="F6" s="2">
-        <v>500</v>
-      </c>
-      <c r="G6" s="2">
-        <v>105</v>
-      </c>
-      <c r="H6" s="2">
-        <v>605</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>